--- a/fomo_two_papers/data/paper2_data.xlsx
+++ b/fomo_two_papers/data/paper2_data.xlsx
@@ -742,7 +742,7 @@
         <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ2" t="n">
         <v>4</v>
@@ -1156,7 +1156,7 @@
         <v>2</v>
       </c>
       <c r="AM5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
         <v>5</v>
@@ -1549,7 +1549,7 @@
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
@@ -1677,7 +1677,7 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -1960,7 +1960,7 @@
         <v>3</v>
       </c>
       <c r="AM11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
         <v>3</v>
@@ -3023,7 +3023,7 @@
         <v>2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
         <v>2</v>
@@ -3431,7 +3431,7 @@
         <v>4</v>
       </c>
       <c r="AL22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM22" t="n">
         <v>3</v>
@@ -3693,10 +3693,10 @@
         <v>3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL24" t="n">
         <v>4</v>
@@ -3824,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ25" t="n">
         <v>3</v>
@@ -3833,7 +3833,7 @@
         <v>3</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>3</v>
@@ -4095,13 +4095,13 @@
         <v>3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK27" t="n">
         <v>4</v>
       </c>
       <c r="AL27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM27" t="n">
         <v>3</v>
@@ -5167,16 +5167,16 @@
         <v>4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL35" t="n">
         <v>2</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN35" t="n">
         <v>4</v>
@@ -6111,7 +6111,7 @@
         <v>5</v>
       </c>
       <c r="AL42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM42" t="n">
         <v>4</v>
@@ -6635,7 +6635,7 @@
         <v>4</v>
       </c>
       <c r="AH46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI46" t="n">
         <v>3</v>
@@ -6644,7 +6644,7 @@
         <v>3</v>
       </c>
       <c r="AK46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL46" t="n">
         <v>4</v>
@@ -6784,7 +6784,7 @@
         <v>3</v>
       </c>
       <c r="AM47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN47" t="n">
         <v>4</v>
@@ -6909,7 +6909,7 @@
         <v>4</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK48" t="n">
         <v>2</v>
@@ -7442,7 +7442,7 @@
         <v>2</v>
       </c>
       <c r="AI52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ52" t="n">
         <v>4</v>
@@ -7588,7 +7588,7 @@
         <v>5</v>
       </c>
       <c r="AM53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN53" t="n">
         <v>4</v>
@@ -8258,7 +8258,7 @@
         <v>2</v>
       </c>
       <c r="AM58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN58" t="n">
         <v>5</v>
@@ -8520,13 +8520,13 @@
         <v>2</v>
       </c>
       <c r="AK60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN60" t="n">
         <v>2</v>
@@ -8782,13 +8782,13 @@
         <v>2</v>
       </c>
       <c r="AI62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL62" t="n">
         <v>2</v>
@@ -9458,10 +9458,10 @@
         <v>4</v>
       </c>
       <c r="AK67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM67" t="n">
         <v>3</v>
@@ -9595,7 +9595,7 @@
         <v>4</v>
       </c>
       <c r="AL68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM68" t="n">
         <v>2</v>
@@ -9866,7 +9866,7 @@
         <v>2</v>
       </c>
       <c r="AM70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN70" t="n">
         <v>4</v>
@@ -10792,16 +10792,16 @@
         <v>4</v>
       </c>
       <c r="AI77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK77" t="n">
         <v>3</v>
       </c>
       <c r="AL77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM77" t="n">
         <v>4</v>
@@ -11194,7 +11194,7 @@
         <v>3</v>
       </c>
       <c r="AI80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ80" t="n">
         <v>4</v>
@@ -11599,7 +11599,7 @@
         <v>5</v>
       </c>
       <c r="AJ83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK83" t="n">
         <v>3</v>
@@ -11736,7 +11736,7 @@
         <v>3</v>
       </c>
       <c r="AK84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL84" t="n">
         <v>2</v>
@@ -12001,7 +12001,7 @@
         <v>3</v>
       </c>
       <c r="AJ86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK86" t="n">
         <v>3</v>
@@ -12409,7 +12409,7 @@
         <v>2</v>
       </c>
       <c r="AL89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM89" t="n">
         <v>3</v>
@@ -12945,7 +12945,7 @@
         <v>1</v>
       </c>
       <c r="AL93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM93" t="n">
         <v>1</v>
@@ -13073,7 +13073,7 @@
         <v>2</v>
       </c>
       <c r="AJ94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK94" t="n">
         <v>2</v>
@@ -13481,7 +13481,7 @@
         <v>2</v>
       </c>
       <c r="AL97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM97" t="n">
         <v>2</v>
@@ -14276,7 +14276,7 @@
         <v>2</v>
       </c>
       <c r="AI103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ103" t="n">
         <v>4</v>
@@ -14550,7 +14550,7 @@
         <v>3</v>
       </c>
       <c r="AK105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL105" t="n">
         <v>4</v>
@@ -15357,7 +15357,7 @@
         <v>3</v>
       </c>
       <c r="AL111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM111" t="n">
         <v>4</v>
@@ -15622,7 +15622,7 @@
         <v>5</v>
       </c>
       <c r="AK113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL113" t="n">
         <v>5</v>
@@ -16295,7 +16295,7 @@
         <v>3</v>
       </c>
       <c r="AL118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM118" t="n">
         <v>3</v>
@@ -16417,7 +16417,7 @@
         <v>3</v>
       </c>
       <c r="AH119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI119" t="n">
         <v>2</v>
@@ -16426,7 +16426,7 @@
         <v>1</v>
       </c>
       <c r="AK119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL119" t="n">
         <v>2</v>
@@ -17093,7 +17093,7 @@
         <v>2</v>
       </c>
       <c r="AJ124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK124" t="n">
         <v>2</v>
@@ -17367,10 +17367,10 @@
         <v>2</v>
       </c>
       <c r="AL126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN126" t="n">
         <v>4</v>
@@ -17629,7 +17629,7 @@
         <v>4</v>
       </c>
       <c r="AJ128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK128" t="n">
         <v>4</v>
@@ -17906,7 +17906,7 @@
         <v>2</v>
       </c>
       <c r="AM130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN130" t="n">
         <v>2</v>
@@ -19103,7 +19103,7 @@
         <v>3</v>
       </c>
       <c r="AJ139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK139" t="n">
         <v>3</v>
@@ -19243,7 +19243,7 @@
         <v>2</v>
       </c>
       <c r="AL140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM140" t="n">
         <v>1</v>
@@ -19776,7 +19776,7 @@
         <v>4</v>
       </c>
       <c r="AK144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL144" t="n">
         <v>4</v>
@@ -19904,19 +19904,19 @@
         <v>2</v>
       </c>
       <c r="AI145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN145" t="n">
         <v>1</v>
@@ -20574,7 +20574,7 @@
         <v>1</v>
       </c>
       <c r="AI150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ150" t="n">
         <v>3</v>
@@ -21390,7 +21390,7 @@
         <v>3</v>
       </c>
       <c r="AM156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN156" t="n">
         <v>5</v>
@@ -21655,7 +21655,7 @@
         <v>2</v>
       </c>
       <c r="AL158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM158" t="n">
         <v>3</v>
@@ -22054,7 +22054,7 @@
         <v>2</v>
       </c>
       <c r="AK161" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL161" t="n">
         <v>2</v>
@@ -22328,7 +22328,7 @@
         <v>4</v>
       </c>
       <c r="AM163" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN163" t="n">
         <v>4</v>
@@ -22456,7 +22456,7 @@
         <v>1</v>
       </c>
       <c r="AK164" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL164" t="n">
         <v>3</v>
@@ -22587,7 +22587,7 @@
         <v>5</v>
       </c>
       <c r="AJ165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK165" t="n">
         <v>5</v>
@@ -22727,7 +22727,7 @@
         <v>2</v>
       </c>
       <c r="AL166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM166" t="n">
         <v>3</v>
@@ -22986,7 +22986,7 @@
         <v>3</v>
       </c>
       <c r="AI168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ168" t="n">
         <v>2</v>
@@ -23120,7 +23120,7 @@
         <v>3</v>
       </c>
       <c r="AI169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ169" t="n">
         <v>1</v>
@@ -23254,7 +23254,7 @@
         <v>3</v>
       </c>
       <c r="AI170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ170" t="n">
         <v>3</v>
@@ -23391,7 +23391,7 @@
         <v>3</v>
       </c>
       <c r="AJ171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK171" t="n">
         <v>2</v>
@@ -24204,7 +24204,7 @@
         <v>3</v>
       </c>
       <c r="AM177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN177" t="n">
         <v>3</v>
@@ -24332,7 +24332,7 @@
         <v>3</v>
       </c>
       <c r="AK178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL178" t="n">
         <v>4</v>
@@ -25133,7 +25133,7 @@
         <v>1</v>
       </c>
       <c r="AJ184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK184" t="n">
         <v>3</v>
@@ -25276,7 +25276,7 @@
         <v>2</v>
       </c>
       <c r="AM185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN185" t="n">
         <v>2</v>
@@ -25395,7 +25395,7 @@
         <v>4</v>
       </c>
       <c r="AH186" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI186" t="n">
         <v>2</v>
@@ -25407,7 +25407,7 @@
         <v>3</v>
       </c>
       <c r="AL186" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM186" t="n">
         <v>2</v>
@@ -25538,7 +25538,7 @@
         <v>3</v>
       </c>
       <c r="AK187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL187" t="n">
         <v>2</v>
@@ -25669,7 +25669,7 @@
         <v>1</v>
       </c>
       <c r="AJ188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK188" t="n">
         <v>1</v>
@@ -25934,7 +25934,7 @@
         <v>3</v>
       </c>
       <c r="AI190" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ190" t="n">
         <v>3</v>
@@ -26339,7 +26339,7 @@
         <v>4</v>
       </c>
       <c r="AJ193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK193" t="n">
         <v>2</v>
@@ -26610,7 +26610,7 @@
         <v>3</v>
       </c>
       <c r="AK195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL195" t="n">
         <v>2</v>
@@ -27012,7 +27012,7 @@
         <v>3</v>
       </c>
       <c r="AK198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL198" t="n">
         <v>1</v>
@@ -27143,16 +27143,16 @@
         <v>2</v>
       </c>
       <c r="AJ199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK199" t="n">
         <v>1</v>
       </c>
       <c r="AL199" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN199" t="n">
         <v>4</v>
@@ -27417,10 +27417,10 @@
         <v>1</v>
       </c>
       <c r="AL201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN201" t="n">
         <v>3</v>
@@ -27551,7 +27551,7 @@
         <v>4</v>
       </c>
       <c r="AL202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM202" t="n">
         <v>3</v>
@@ -28084,7 +28084,7 @@
         <v>3</v>
       </c>
       <c r="AK206" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL206" t="n">
         <v>4</v>
@@ -28218,7 +28218,7 @@
         <v>4</v>
       </c>
       <c r="AK207" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL207" t="n">
         <v>5</v>
@@ -28614,7 +28614,7 @@
         <v>2</v>
       </c>
       <c r="AI210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ210" t="n">
         <v>1</v>
@@ -28882,19 +28882,19 @@
         <v>2</v>
       </c>
       <c r="AI212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ212" t="n">
         <v>1</v>
       </c>
       <c r="AK212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL212" t="n">
         <v>1</v>
       </c>
       <c r="AM212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN212" t="n">
         <v>4</v>
@@ -29287,7 +29287,7 @@
         <v>1</v>
       </c>
       <c r="AJ215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK215" t="n">
         <v>2</v>
@@ -29552,13 +29552,13 @@
         <v>1</v>
       </c>
       <c r="AI217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ217" t="n">
         <v>3</v>
       </c>
       <c r="AK217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL217" t="n">
         <v>3</v>
@@ -29698,7 +29698,7 @@
         <v>4</v>
       </c>
       <c r="AM218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN218" t="n">
         <v>2</v>
@@ -30097,7 +30097,7 @@
         <v>2</v>
       </c>
       <c r="AL221" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM221" t="n">
         <v>2</v>
@@ -31160,7 +31160,7 @@
         <v>4</v>
       </c>
       <c r="AI229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ229" t="n">
         <v>1</v>
@@ -31172,7 +31172,7 @@
         <v>3</v>
       </c>
       <c r="AM229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN229" t="n">
         <v>2</v>
@@ -31434,10 +31434,10 @@
         <v>2</v>
       </c>
       <c r="AK231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL231" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM231" t="n">
         <v>2</v>
@@ -32098,7 +32098,7 @@
         <v>2</v>
       </c>
       <c r="AI236" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ236" t="n">
         <v>3</v>
@@ -32107,7 +32107,7 @@
         <v>2</v>
       </c>
       <c r="AL236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM236" t="n">
         <v>3</v>
@@ -32238,13 +32238,13 @@
         <v>2</v>
       </c>
       <c r="AK237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN237" t="n">
         <v>4</v>
@@ -32366,7 +32366,7 @@
         <v>2</v>
       </c>
       <c r="AI238" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ238" t="n">
         <v>1</v>
@@ -32500,13 +32500,13 @@
         <v>5</v>
       </c>
       <c r="AI239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL239" t="n">
         <v>3</v>
@@ -33304,13 +33304,13 @@
         <v>2</v>
       </c>
       <c r="AI245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ245" t="n">
         <v>1</v>
       </c>
       <c r="AK245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL245" t="n">
         <v>2</v>
@@ -33441,7 +33441,7 @@
         <v>3</v>
       </c>
       <c r="AJ246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK246" t="n">
         <v>2</v>
@@ -33706,7 +33706,7 @@
         <v>2</v>
       </c>
       <c r="AI248" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ248" t="n">
         <v>4</v>
@@ -34114,7 +34114,7 @@
         <v>3</v>
       </c>
       <c r="AK251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL251" t="n">
         <v>3</v>
@@ -34254,7 +34254,7 @@
         <v>5</v>
       </c>
       <c r="AM252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN252" t="n">
         <v>4</v>
@@ -34653,7 +34653,7 @@
         <v>2</v>
       </c>
       <c r="AL255" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM255" t="n">
         <v>4</v>
@@ -34787,10 +34787,10 @@
         <v>3</v>
       </c>
       <c r="AL256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM256" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN256" t="n">
         <v>2</v>
@@ -34921,7 +34921,7 @@
         <v>3</v>
       </c>
       <c r="AL257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM257" t="n">
         <v>5</v>
@@ -35451,7 +35451,7 @@
         <v>4</v>
       </c>
       <c r="AJ261" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK261" t="n">
         <v>3</v>
@@ -35588,7 +35588,7 @@
         <v>2</v>
       </c>
       <c r="AK262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL262" t="n">
         <v>2</v>
@@ -35987,7 +35987,7 @@
         <v>3</v>
       </c>
       <c r="AJ265" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK265" t="n">
         <v>3</v>
@@ -36127,7 +36127,7 @@
         <v>1</v>
       </c>
       <c r="AL266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM266" t="n">
         <v>1</v>
@@ -36386,7 +36386,7 @@
         <v>2</v>
       </c>
       <c r="AI268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ268" t="n">
         <v>1</v>
@@ -37202,7 +37202,7 @@
         <v>4</v>
       </c>
       <c r="AM274" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN274" t="n">
         <v>2</v>
@@ -37601,7 +37601,7 @@
         <v>4</v>
       </c>
       <c r="AL277" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM277" t="n">
         <v>4</v>
@@ -37735,7 +37735,7 @@
         <v>2</v>
       </c>
       <c r="AL278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM278" t="n">
         <v>2</v>
@@ -37857,7 +37857,7 @@
         <v>4</v>
       </c>
       <c r="AH279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI279" t="n">
         <v>3</v>
@@ -37869,7 +37869,7 @@
         <v>2</v>
       </c>
       <c r="AL279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM279" t="n">
         <v>5</v>
@@ -38542,7 +38542,7 @@
         <v>2</v>
       </c>
       <c r="AM284" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN284" t="n">
         <v>4</v>
@@ -38932,7 +38932,7 @@
         <v>3</v>
       </c>
       <c r="AI287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ287" t="n">
         <v>3</v>
@@ -38944,7 +38944,7 @@
         <v>3</v>
       </c>
       <c r="AM287" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN287" t="n">
         <v>5</v>
@@ -39203,7 +39203,7 @@
         <v>2</v>
       </c>
       <c r="AJ289" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK289" t="n">
         <v>2</v>
@@ -39340,7 +39340,7 @@
         <v>3</v>
       </c>
       <c r="AK290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL290" t="n">
         <v>4</v>
@@ -39879,7 +39879,7 @@
         <v>2</v>
       </c>
       <c r="AL294" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM294" t="n">
         <v>3</v>
@@ -40412,7 +40412,7 @@
         <v>3</v>
       </c>
       <c r="AK298" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL298" t="n">
         <v>2</v>
@@ -40543,13 +40543,13 @@
         <v>3</v>
       </c>
       <c r="AJ299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK299" t="n">
         <v>2</v>
       </c>
       <c r="AL299" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM299" t="n">
         <v>4</v>
@@ -40817,7 +40817,7 @@
         <v>3</v>
       </c>
       <c r="AL301" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM301" t="n">
         <v>3</v>
@@ -40945,7 +40945,7 @@
         <v>2</v>
       </c>
       <c r="AJ302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK302" t="n">
         <v>2</v>
@@ -41079,7 +41079,7 @@
         <v>2</v>
       </c>
       <c r="AJ303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK303" t="n">
         <v>2</v>
@@ -41222,7 +41222,7 @@
         <v>4</v>
       </c>
       <c r="AM304" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN304" t="n">
         <v>2</v>
@@ -42017,7 +42017,7 @@
         <v>4</v>
       </c>
       <c r="AJ310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK310" t="n">
         <v>3</v>
@@ -42285,7 +42285,7 @@
         <v>4</v>
       </c>
       <c r="AJ312" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK312" t="n">
         <v>4</v>
@@ -42416,7 +42416,7 @@
         <v>2</v>
       </c>
       <c r="AI313" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ313" t="n">
         <v>3</v>
@@ -42690,7 +42690,7 @@
         <v>2</v>
       </c>
       <c r="AK315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL315" t="n">
         <v>3</v>
@@ -44161,16 +44161,16 @@
         <v>4</v>
       </c>
       <c r="AJ326" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK326" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL326" t="n">
         <v>4</v>
       </c>
       <c r="AM326" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN326" t="n">
         <v>3</v>
@@ -44295,7 +44295,7 @@
         <v>3</v>
       </c>
       <c r="AJ327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK327" t="n">
         <v>2</v>
@@ -44566,7 +44566,7 @@
         <v>4</v>
       </c>
       <c r="AK329" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL329" t="n">
         <v>3</v>
@@ -44962,7 +44962,7 @@
         <v>1</v>
       </c>
       <c r="AI332" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ332" t="n">
         <v>3</v>
@@ -45099,7 +45099,7 @@
         <v>3</v>
       </c>
       <c r="AJ333" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK333" t="n">
         <v>2</v>
@@ -45233,7 +45233,7 @@
         <v>2</v>
       </c>
       <c r="AJ334" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK334" t="n">
         <v>2</v>
@@ -46308,13 +46308,13 @@
         <v>4</v>
       </c>
       <c r="AK342" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL342" t="n">
         <v>3</v>
       </c>
       <c r="AM342" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN342" t="n">
         <v>2</v>
@@ -46436,7 +46436,7 @@
         <v>2</v>
       </c>
       <c r="AI343" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ343" t="n">
         <v>3</v>
@@ -46576,7 +46576,7 @@
         <v>2</v>
       </c>
       <c r="AK344" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL344" t="n">
         <v>4</v>
@@ -46847,7 +46847,7 @@
         <v>1</v>
       </c>
       <c r="AL346" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM346" t="n">
         <v>2</v>
@@ -48053,7 +48053,7 @@
         <v>3</v>
       </c>
       <c r="AL355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM355" t="n">
         <v>4</v>
@@ -48187,7 +48187,7 @@
         <v>2</v>
       </c>
       <c r="AL356" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM356" t="n">
         <v>3</v>
@@ -48851,16 +48851,16 @@
         <v>1</v>
       </c>
       <c r="AJ361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK361" t="n">
         <v>3</v>
       </c>
       <c r="AL361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM361" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN361" t="n">
         <v>4</v>
@@ -49256,10 +49256,10 @@
         <v>1</v>
       </c>
       <c r="AK364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM364" t="n">
         <v>2</v>
@@ -49652,7 +49652,7 @@
         <v>2</v>
       </c>
       <c r="AI367" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ367" t="n">
         <v>5</v>
@@ -50185,10 +50185,10 @@
         <v>1</v>
       </c>
       <c r="AH371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI371" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ371" t="n">
         <v>3</v>
@@ -50334,7 +50334,7 @@
         <v>4</v>
       </c>
       <c r="AM372" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN372" t="n">
         <v>4</v>
@@ -50593,7 +50593,7 @@
         <v>4</v>
       </c>
       <c r="AJ374" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK374" t="n">
         <v>2</v>
@@ -50736,7 +50736,7 @@
         <v>3</v>
       </c>
       <c r="AM375" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN375" t="n">
         <v>2</v>
@@ -50995,7 +50995,7 @@
         <v>4</v>
       </c>
       <c r="AJ377" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK377" t="n">
         <v>4</v>
@@ -51004,7 +51004,7 @@
         <v>4</v>
       </c>
       <c r="AM377" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN377" t="n">
         <v>1</v>
@@ -51662,7 +51662,7 @@
         <v>2</v>
       </c>
       <c r="AI382" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ382" t="n">
         <v>3</v>
@@ -51671,7 +51671,7 @@
         <v>3</v>
       </c>
       <c r="AL382" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM382" t="n">
         <v>3</v>
@@ -51808,7 +51808,7 @@
         <v>2</v>
       </c>
       <c r="AM383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN383" t="n">
         <v>5</v>
@@ -52335,7 +52335,7 @@
         <v>2</v>
       </c>
       <c r="AJ387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK387" t="n">
         <v>1</v>
@@ -52463,7 +52463,7 @@
         <v>2</v>
       </c>
       <c r="AH388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI388" t="n">
         <v>3</v>
@@ -52475,10 +52475,10 @@
         <v>1</v>
       </c>
       <c r="AL388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM388" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN388" t="n">
         <v>4</v>
@@ -52737,7 +52737,7 @@
         <v>3</v>
       </c>
       <c r="AJ390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK390" t="n">
         <v>3</v>
@@ -53014,7 +53014,7 @@
         <v>2</v>
       </c>
       <c r="AM392" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN392" t="n">
         <v>3</v>
@@ -53550,7 +53550,7 @@
         <v>4</v>
       </c>
       <c r="AM396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN396" t="n">
         <v>5</v>
@@ -53943,7 +53943,7 @@
         <v>4</v>
       </c>
       <c r="AJ399" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK399" t="n">
         <v>3</v>
@@ -53952,7 +53952,7 @@
         <v>5</v>
       </c>
       <c r="AM399" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN399" t="n">
         <v>5</v>
@@ -54211,7 +54211,7 @@
         <v>1</v>
       </c>
       <c r="AJ401" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK401" t="n">
         <v>1</v>
@@ -54476,7 +54476,7 @@
         <v>1</v>
       </c>
       <c r="AI403" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ403" t="n">
         <v>4</v>
@@ -54881,16 +54881,16 @@
         <v>2</v>
       </c>
       <c r="AJ406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL406" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM406" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN406" t="n">
         <v>5</v>
@@ -55146,7 +55146,7 @@
         <v>2</v>
       </c>
       <c r="AI408" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ408" t="n">
         <v>3</v>
@@ -55417,7 +55417,7 @@
         <v>4</v>
       </c>
       <c r="AJ410" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK410" t="n">
         <v>3</v>
@@ -55816,7 +55816,7 @@
         <v>4</v>
       </c>
       <c r="AI413" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ413" t="n">
         <v>3</v>
@@ -55828,7 +55828,7 @@
         <v>4</v>
       </c>
       <c r="AM413" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN413" t="n">
         <v>2</v>
@@ -55953,7 +55953,7 @@
         <v>3</v>
       </c>
       <c r="AJ414" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK414" t="n">
         <v>3</v>
@@ -56623,7 +56623,7 @@
         <v>2</v>
       </c>
       <c r="AJ419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK419" t="n">
         <v>2</v>
@@ -56891,7 +56891,7 @@
         <v>2</v>
       </c>
       <c r="AJ421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK421" t="n">
         <v>1</v>
@@ -57558,7 +57558,7 @@
         <v>1</v>
       </c>
       <c r="AI426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ426" t="n">
         <v>5</v>
@@ -57567,10 +57567,10 @@
         <v>4</v>
       </c>
       <c r="AL426" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM426" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN426" t="n">
         <v>4</v>
@@ -57826,7 +57826,7 @@
         <v>1</v>
       </c>
       <c r="AI428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ428" t="n">
         <v>2</v>
@@ -57835,7 +57835,7 @@
         <v>1</v>
       </c>
       <c r="AL428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM428" t="n">
         <v>1</v>
@@ -57960,7 +57960,7 @@
         <v>4</v>
       </c>
       <c r="AI429" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ429" t="n">
         <v>2</v>
@@ -58642,7 +58642,7 @@
         <v>3</v>
       </c>
       <c r="AM434" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN434" t="n">
         <v>3</v>
@@ -58910,7 +58910,7 @@
         <v>3</v>
       </c>
       <c r="AM436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN436" t="n">
         <v>3</v>
@@ -59169,7 +59169,7 @@
         <v>2</v>
       </c>
       <c r="AJ438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK438" t="n">
         <v>2</v>
@@ -59446,7 +59446,7 @@
         <v>2</v>
       </c>
       <c r="AM440" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN440" t="n">
         <v>2</v>
@@ -59577,7 +59577,7 @@
         <v>1</v>
       </c>
       <c r="AL441" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM441" t="n">
         <v>1</v>
